--- a/data/trans_bre/P8_1_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P8_1_R-Edad-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,96</t>
+          <t>-0,92; 2,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 3,94</t>
+          <t>-0,23; 4,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,44</t>
+          <t>0,81; 4,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 0,98</t>
+          <t>-4,72; 0,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-38,83; 397,9</t>
+          <t>-44,04; 312,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 446,86</t>
+          <t>-19,39; 409,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; —</t>
+          <t>-13,86; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 4,09</t>
+          <t>-0,35; 4,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,46</t>
+          <t>-1,24; 3,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 3,5</t>
+          <t>-1,23; 3,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,05; -1,62</t>
+          <t>-7,71; -1,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 178,2</t>
+          <t>-12,44; 171,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 135,05</t>
+          <t>-30,39; 156,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,43; 171,7</t>
+          <t>-28,74; 153,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-92,79; -41,71</t>
+          <t>-94,62; -39,59</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,23</t>
+          <t>1,07; 6,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 8,48</t>
+          <t>2,09; 8,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 5,08</t>
+          <t>-0,17; 5,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 4,05</t>
+          <t>-1,74; 4,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,2; 199,29</t>
+          <t>18,97; 212,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,07; 175,89</t>
+          <t>25,91; 163,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 130,85</t>
+          <t>-5,76; 137,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,36; 99,57</t>
+          <t>-23,04; 108,29</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 11,94</t>
+          <t>4,04; 11,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 9,7</t>
+          <t>1,55; 9,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 8,02</t>
+          <t>0,24; 7,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-62,85; 3,41</t>
+          <t>-55,28; 3,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,61; 207,79</t>
+          <t>44,4; 204,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,74; 104,66</t>
+          <t>11,1; 106,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 84,59</t>
+          <t>2,34; 83,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-83,29; 31,44</t>
+          <t>-81,62; 37,83</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 13,27</t>
+          <t>1,96; 13,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,74; 24,35</t>
+          <t>11,79; 23,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,84; 18,46</t>
+          <t>6,56; 18,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 8,9</t>
+          <t>0,5; 8,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,51; 75,03</t>
+          <t>8,0; 79,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,29; 149,25</t>
+          <t>50,73; 143,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,75; 113,67</t>
+          <t>29,73; 118,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 48,71</t>
+          <t>1,28; 49,91</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,53; 32,5</t>
+          <t>19,31; 32,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,49; 27,23</t>
+          <t>11,73; 27,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,74; 23,04</t>
+          <t>9,06; 22,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 17,24</t>
+          <t>-13,19; 16,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>59,86; 141,78</t>
+          <t>61,88; 139,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,87; 88,92</t>
+          <t>29,74; 93,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,24; 86,23</t>
+          <t>26,97; 87,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-52,46; 78,86</t>
+          <t>-51,74; 77,22</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,59; 30,89</t>
+          <t>14,02; 31,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,08; 21,27</t>
+          <t>6,23; 21,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,66; 22,12</t>
+          <t>6,29; 21,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,78; 29,71</t>
+          <t>18,53; 29,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,82; 65,25</t>
+          <t>24,29; 67,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,33; 34,64</t>
+          <t>8,56; 35,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,12; 41,85</t>
+          <t>10,29; 42,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34,9; 64,74</t>
+          <t>33,76; 63,39</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,48; 12,04</t>
+          <t>8,41; 12,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,73; 12,67</t>
+          <t>8,66; 12,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,93; 10,62</t>
+          <t>7,08; 10,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 6,37</t>
+          <t>-17,8; 6,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>71,36; 115,43</t>
+          <t>70,26; 115,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>56,04; 92,82</t>
+          <t>55,61; 92,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,66; 81,36</t>
+          <t>48,08; 82,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-52,8; 43,65</t>
+          <t>-46,88; 46,51</t>
         </is>
       </c>
     </row>
